--- a/backend/data/financials_by_company/0411.HK.xlsx
+++ b/backend/data/financials_by_company/0411.HK.xlsx
@@ -652,556 +652,556 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>159793.675912</v>
+        <v>-1358501.484244</v>
       </c>
       <c r="C2" t="n">
-        <v>0.179745</v>
+        <v>0.149862</v>
       </c>
       <c r="D2" t="n">
-        <v>316323000</v>
+        <v>493015000</v>
       </c>
       <c r="E2" t="n">
-        <v>889000</v>
+        <v>-9065000</v>
       </c>
       <c r="F2" t="n">
-        <v>889000</v>
+        <v>-9065000</v>
       </c>
       <c r="G2" t="n">
-        <v>200599000</v>
+        <v>357698000</v>
       </c>
       <c r="H2" t="n">
-        <v>72401000</v>
+        <v>62914000</v>
       </c>
       <c r="I2" t="n">
-        <v>3824687000</v>
+        <v>4476856000</v>
       </c>
       <c r="J2" t="n">
-        <v>317212000</v>
+        <v>483950000</v>
       </c>
       <c r="K2" t="n">
-        <v>244811000</v>
+        <v>421036000</v>
       </c>
       <c r="L2" t="n">
-        <v>44405000</v>
+        <v>26481000</v>
       </c>
       <c r="M2" t="n">
-        <v>254000</v>
+        <v>283000</v>
       </c>
       <c r="N2" t="n">
-        <v>44659000</v>
+        <v>26764000</v>
       </c>
       <c r="O2" t="n">
-        <v>199869793.675912</v>
+        <v>365404498.515756</v>
       </c>
       <c r="P2" t="n">
-        <v>200599000</v>
+        <v>357698000</v>
       </c>
       <c r="Q2" t="n">
-        <v>4647009000</v>
+        <v>5368651000</v>
       </c>
       <c r="R2" t="n">
-        <v>244811000</v>
+        <v>421036000</v>
       </c>
       <c r="S2" t="n">
-        <v>234854000</v>
+        <v>236875000</v>
       </c>
       <c r="T2" t="n">
-        <v>234854000</v>
+        <v>236875000</v>
       </c>
       <c r="U2" t="n">
-        <v>0.85</v>
+        <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>0.85</v>
+        <v>1.51</v>
       </c>
       <c r="W2" t="n">
-        <v>200599000</v>
+        <v>357698000</v>
       </c>
       <c r="X2" t="n">
-        <v>200599000</v>
+        <v>357698000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>200599000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>357698000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
       <c r="AB2" t="n">
-        <v>200599000</v>
+        <v>357698000</v>
       </c>
       <c r="AC2" t="n">
-        <v>200599000</v>
+        <v>357698000</v>
       </c>
       <c r="AD2" t="n">
-        <v>43958000</v>
+        <v>63055000</v>
       </c>
       <c r="AE2" t="n">
-        <v>244557000</v>
+        <v>420753000</v>
       </c>
       <c r="AF2" t="n">
-        <v>2048000</v>
+        <v>4575000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-2000</v>
+        <v>-2608000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2000</v>
+        <v>2608000</v>
       </c>
       <c r="AI2" t="n">
-        <v>44405000</v>
+        <v>26481000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>254000</v>
+        <v>283000</v>
       </c>
       <c r="AK2" t="n">
-        <v>44659000</v>
+        <v>26764000</v>
       </c>
       <c r="AL2" t="n">
-        <v>190576000</v>
+        <v>392597000</v>
       </c>
       <c r="AM2" t="n">
-        <v>822322000</v>
+        <v>891795000</v>
       </c>
       <c r="AN2" t="n">
-        <v>826214000</v>
+        <v>909322000</v>
       </c>
       <c r="AO2" t="n">
-        <v>625049000</v>
+        <v>711441000</v>
       </c>
       <c r="AP2" t="n">
-        <v>201165000</v>
+        <v>197881000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1012898000</v>
+        <v>1284392000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3824687000</v>
+        <v>4476856000</v>
       </c>
       <c r="AS2" t="n">
-        <v>4837585000</v>
+        <v>5761248000</v>
       </c>
       <c r="AT2" t="n">
-        <v>4837585000</v>
+        <v>5761248000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>31076.812666</v>
+        <v>133733.564329</v>
       </c>
       <c r="C3" t="n">
-        <v>0.057656</v>
+        <v>0.09869600000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>166875000</v>
+        <v>350349000</v>
       </c>
       <c r="E3" t="n">
-        <v>539000</v>
+        <v>1355000</v>
       </c>
       <c r="F3" t="n">
-        <v>539000</v>
+        <v>1355000</v>
       </c>
       <c r="G3" t="n">
-        <v>85349000</v>
+        <v>257260000</v>
       </c>
       <c r="H3" t="n">
-        <v>76635000</v>
+        <v>65977000</v>
       </c>
       <c r="I3" t="n">
-        <v>4242965000</v>
+        <v>4963246000</v>
       </c>
       <c r="J3" t="n">
-        <v>167414000</v>
+        <v>351704000</v>
       </c>
       <c r="K3" t="n">
-        <v>90779000</v>
+        <v>285727000</v>
       </c>
       <c r="L3" t="n">
-        <v>32420000</v>
+        <v>24379000</v>
       </c>
       <c r="M3" t="n">
-        <v>208000</v>
+        <v>296000</v>
       </c>
       <c r="N3" t="n">
-        <v>32628000</v>
+        <v>24675000</v>
       </c>
       <c r="O3" t="n">
-        <v>84841076.812666</v>
+        <v>256038733.564329</v>
       </c>
       <c r="P3" t="n">
-        <v>85349000</v>
+        <v>257260000</v>
       </c>
       <c r="Q3" t="n">
-        <v>5069718000</v>
+        <v>5855521000</v>
       </c>
       <c r="R3" t="n">
-        <v>90779000</v>
+        <v>285727000</v>
       </c>
       <c r="S3" t="n">
-        <v>234981000</v>
+        <v>235726000</v>
       </c>
       <c r="T3" t="n">
-        <v>234981000</v>
+        <v>235726000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.36</v>
+        <v>1.09</v>
       </c>
       <c r="V3" t="n">
-        <v>0.36</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>85349000</v>
+        <v>257260000</v>
       </c>
       <c r="X3" t="n">
-        <v>85349000</v>
+        <v>257260000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>85349000</v>
+        <v>257260000</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>85349000</v>
+        <v>257260000</v>
       </c>
       <c r="AC3" t="n">
-        <v>85349000</v>
+        <v>257260000</v>
       </c>
       <c r="AD3" t="n">
-        <v>5222000</v>
+        <v>28171000</v>
       </c>
       <c r="AE3" t="n">
-        <v>90571000</v>
+        <v>285431000</v>
       </c>
       <c r="AF3" t="n">
-        <v>3201000</v>
+        <v>5947000</v>
       </c>
       <c r="AG3" t="n">
-        <v>539000</v>
+        <v>127000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-539000</v>
+        <v>-127000</v>
       </c>
       <c r="AI3" t="n">
-        <v>32420000</v>
+        <v>24379000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>208000</v>
+        <v>296000</v>
       </c>
       <c r="AK3" t="n">
-        <v>32628000</v>
+        <v>24675000</v>
       </c>
       <c r="AL3" t="n">
-        <v>49220000</v>
+        <v>251114000</v>
       </c>
       <c r="AM3" t="n">
-        <v>826753000</v>
+        <v>892275000</v>
       </c>
       <c r="AN3" t="n">
-        <v>830380000</v>
+        <v>897855000</v>
       </c>
       <c r="AO3" t="n">
-        <v>641384000</v>
+        <v>694554000</v>
       </c>
       <c r="AP3" t="n">
-        <v>188996000</v>
+        <v>203301000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>875973000</v>
+        <v>1143389000</v>
       </c>
       <c r="AR3" t="n">
-        <v>4242965000</v>
+        <v>4963246000</v>
       </c>
       <c r="AS3" t="n">
-        <v>5118938000</v>
+        <v>6106635000</v>
       </c>
       <c r="AT3" t="n">
-        <v>5118938000</v>
+        <v>6106635000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>133733.564329</v>
+        <v>31076.812666</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09869600000000001</v>
+        <v>0.057656</v>
       </c>
       <c r="D4" t="n">
-        <v>350349000</v>
+        <v>166875000</v>
       </c>
       <c r="E4" t="n">
-        <v>1355000</v>
+        <v>539000</v>
       </c>
       <c r="F4" t="n">
-        <v>1355000</v>
+        <v>539000</v>
       </c>
       <c r="G4" t="n">
-        <v>257260000</v>
+        <v>85349000</v>
       </c>
       <c r="H4" t="n">
-        <v>65977000</v>
+        <v>76635000</v>
       </c>
       <c r="I4" t="n">
-        <v>4963246000</v>
+        <v>4242965000</v>
       </c>
       <c r="J4" t="n">
-        <v>351704000</v>
+        <v>167414000</v>
       </c>
       <c r="K4" t="n">
-        <v>285727000</v>
+        <v>90779000</v>
       </c>
       <c r="L4" t="n">
-        <v>24379000</v>
+        <v>32420000</v>
       </c>
       <c r="M4" t="n">
-        <v>296000</v>
+        <v>208000</v>
       </c>
       <c r="N4" t="n">
-        <v>24675000</v>
+        <v>32628000</v>
       </c>
       <c r="O4" t="n">
-        <v>256038733.564329</v>
+        <v>84841076.812666</v>
       </c>
       <c r="P4" t="n">
-        <v>257260000</v>
+        <v>85349000</v>
       </c>
       <c r="Q4" t="n">
-        <v>5855521000</v>
+        <v>5069718000</v>
       </c>
       <c r="R4" t="n">
-        <v>285727000</v>
+        <v>90779000</v>
       </c>
       <c r="S4" t="n">
-        <v>235726000</v>
+        <v>234981000</v>
       </c>
       <c r="T4" t="n">
-        <v>235726000</v>
+        <v>234981000</v>
       </c>
       <c r="U4" t="n">
-        <v>1.09</v>
+        <v>0.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>0.36</v>
       </c>
       <c r="W4" t="n">
-        <v>257260000</v>
+        <v>85349000</v>
       </c>
       <c r="X4" t="n">
-        <v>257260000</v>
+        <v>85349000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>257260000</v>
+        <v>85349000</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>257260000</v>
+        <v>85349000</v>
       </c>
       <c r="AC4" t="n">
-        <v>257260000</v>
+        <v>85349000</v>
       </c>
       <c r="AD4" t="n">
-        <v>28171000</v>
+        <v>5222000</v>
       </c>
       <c r="AE4" t="n">
-        <v>285431000</v>
+        <v>90571000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5947000</v>
+        <v>3201000</v>
       </c>
       <c r="AG4" t="n">
-        <v>127000</v>
+        <v>539000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-127000</v>
+        <v>-539000</v>
       </c>
       <c r="AI4" t="n">
-        <v>24379000</v>
+        <v>32420000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>296000</v>
+        <v>208000</v>
       </c>
       <c r="AK4" t="n">
-        <v>24675000</v>
+        <v>32628000</v>
       </c>
       <c r="AL4" t="n">
-        <v>251114000</v>
+        <v>49220000</v>
       </c>
       <c r="AM4" t="n">
-        <v>892275000</v>
+        <v>826753000</v>
       </c>
       <c r="AN4" t="n">
-        <v>897855000</v>
+        <v>830380000</v>
       </c>
       <c r="AO4" t="n">
-        <v>694554000</v>
+        <v>641384000</v>
       </c>
       <c r="AP4" t="n">
-        <v>203301000</v>
+        <v>188996000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1143389000</v>
+        <v>875973000</v>
       </c>
       <c r="AR4" t="n">
-        <v>4963246000</v>
+        <v>4242965000</v>
       </c>
       <c r="AS4" t="n">
-        <v>6106635000</v>
+        <v>5118938000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6106635000</v>
+        <v>5118938000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-1358501.484244</v>
+        <v>159793.675912</v>
       </c>
       <c r="C5" t="n">
-        <v>0.149862</v>
+        <v>0.179745</v>
       </c>
       <c r="D5" t="n">
-        <v>493015000</v>
+        <v>316323000</v>
       </c>
       <c r="E5" t="n">
-        <v>-9065000</v>
+        <v>889000</v>
       </c>
       <c r="F5" t="n">
-        <v>-9065000</v>
+        <v>889000</v>
       </c>
       <c r="G5" t="n">
-        <v>357698000</v>
+        <v>200599000</v>
       </c>
       <c r="H5" t="n">
-        <v>62914000</v>
+        <v>72401000</v>
       </c>
       <c r="I5" t="n">
-        <v>4476856000</v>
+        <v>3824687000</v>
       </c>
       <c r="J5" t="n">
-        <v>483950000</v>
+        <v>317212000</v>
       </c>
       <c r="K5" t="n">
-        <v>421036000</v>
+        <v>244811000</v>
       </c>
       <c r="L5" t="n">
-        <v>26481000</v>
+        <v>44405000</v>
       </c>
       <c r="M5" t="n">
-        <v>283000</v>
+        <v>254000</v>
       </c>
       <c r="N5" t="n">
-        <v>26764000</v>
+        <v>44659000</v>
       </c>
       <c r="O5" t="n">
-        <v>365404498.515756</v>
+        <v>199869793.675912</v>
       </c>
       <c r="P5" t="n">
-        <v>357698000</v>
+        <v>200599000</v>
       </c>
       <c r="Q5" t="n">
-        <v>5368651000</v>
+        <v>4647009000</v>
       </c>
       <c r="R5" t="n">
-        <v>421036000</v>
+        <v>244811000</v>
       </c>
       <c r="S5" t="n">
-        <v>236875000</v>
+        <v>234854000</v>
       </c>
       <c r="T5" t="n">
-        <v>236875000</v>
+        <v>234854000</v>
       </c>
       <c r="U5" t="n">
-        <v>1.51</v>
+        <v>0.85</v>
       </c>
       <c r="V5" t="n">
-        <v>1.51</v>
+        <v>0.85</v>
       </c>
       <c r="W5" t="n">
-        <v>357698000</v>
+        <v>200599000</v>
       </c>
       <c r="X5" t="n">
-        <v>357698000</v>
+        <v>200599000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>357698000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
+        <v>200599000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>357698000</v>
+        <v>200599000</v>
       </c>
       <c r="AC5" t="n">
-        <v>357698000</v>
+        <v>200599000</v>
       </c>
       <c r="AD5" t="n">
-        <v>63055000</v>
+        <v>43958000</v>
       </c>
       <c r="AE5" t="n">
-        <v>420753000</v>
+        <v>244557000</v>
       </c>
       <c r="AF5" t="n">
-        <v>4575000</v>
+        <v>2048000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2608000</v>
+        <v>-2000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2608000</v>
+        <v>2000</v>
       </c>
       <c r="AI5" t="n">
-        <v>26481000</v>
+        <v>44405000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>283000</v>
+        <v>254000</v>
       </c>
       <c r="AK5" t="n">
-        <v>26764000</v>
+        <v>44659000</v>
       </c>
       <c r="AL5" t="n">
-        <v>392597000</v>
+        <v>190576000</v>
       </c>
       <c r="AM5" t="n">
-        <v>891795000</v>
+        <v>822322000</v>
       </c>
       <c r="AN5" t="n">
-        <v>909322000</v>
+        <v>826214000</v>
       </c>
       <c r="AO5" t="n">
-        <v>711441000</v>
+        <v>625049000</v>
       </c>
       <c r="AP5" t="n">
-        <v>197881000</v>
+        <v>201165000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1284392000</v>
+        <v>1012898000</v>
       </c>
       <c r="AR5" t="n">
-        <v>4476856000</v>
+        <v>3824687000</v>
       </c>
       <c r="AS5" t="n">
-        <v>5761248000</v>
+        <v>4837585000</v>
       </c>
       <c r="AT5" t="n">
-        <v>5761248000</v>
+        <v>4837585000</v>
       </c>
     </row>
   </sheetData>
@@ -1527,53 +1527,47 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
-      </c>
-      <c r="B2" t="n">
-        <v>8583000</v>
-      </c>
+        <v>44377</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>234822000</v>
+        <v>243354000</v>
       </c>
       <c r="D2" t="n">
         <v>243354000</v>
       </c>
       <c r="E2" t="n">
-        <v>3948000</v>
+        <v>5212000</v>
       </c>
       <c r="F2" t="n">
-        <v>2895693000</v>
+        <v>2875466000</v>
       </c>
       <c r="G2" t="n">
-        <v>2904223000</v>
+        <v>2880665000</v>
       </c>
       <c r="H2" t="n">
-        <v>2116164000</v>
+        <v>1980576000</v>
       </c>
       <c r="I2" t="n">
-        <v>2895693000</v>
+        <v>2875466000</v>
       </c>
       <c r="J2" t="n">
-        <v>3948000</v>
+        <v>5212000</v>
       </c>
       <c r="K2" t="n">
-        <v>2904223000</v>
+        <v>2880665000</v>
       </c>
       <c r="L2" t="n">
-        <v>2904223000</v>
+        <v>2880665000</v>
       </c>
       <c r="M2" t="n">
-        <v>2904223000</v>
+        <v>2880665000</v>
       </c>
       <c r="N2" t="n">
-        <v>2904223000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-85104000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>187830000</v>
-      </c>
+        <v>2880665000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>672777000</v>
       </c>
@@ -1581,182 +1575,180 @@
         <v>672777000</v>
       </c>
       <c r="S2" t="n">
-        <v>642374000</v>
+        <v>794877000</v>
       </c>
       <c r="T2" t="n">
-        <v>24179000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1943000</v>
-      </c>
+        <v>17093000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>20903000</v>
+        <v>15246000</v>
       </c>
       <c r="W2" t="n">
-        <v>1333000</v>
+        <v>1847000</v>
       </c>
       <c r="X2" t="n">
-        <v>1333000</v>
+        <v>1847000</v>
       </c>
       <c r="Y2" t="n">
-        <v>618195000</v>
+        <v>777784000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2615000</v>
+        <v>3365000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2615000</v>
+        <v>3365000</v>
       </c>
       <c r="AB2" t="n">
-        <v>595459000</v>
+        <v>733338000</v>
       </c>
       <c r="AC2" t="n">
-        <v>274193000</v>
+        <v>312560000</v>
       </c>
       <c r="AD2" t="n">
-        <v>17389000</v>
+        <v>12772000</v>
       </c>
       <c r="AE2" t="n">
-        <v>303877000</v>
+        <v>408006000</v>
       </c>
       <c r="AF2" t="n">
-        <v>3546597000</v>
+        <v>3675542000</v>
       </c>
       <c r="AG2" t="n">
-        <v>812238000</v>
+        <v>917182000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1702000</v>
+        <v>4250000</v>
       </c>
       <c r="AI2" t="n">
-        <v>11897000</v>
+        <v>672000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>52364000</v>
+        <v>82760000</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>52092000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>81945000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>815000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>8530000</v>
+        <v>5199000</v>
       </c>
       <c r="AO2" t="n">
-        <v>6355000</v>
+        <v>3024000</v>
       </c>
       <c r="AP2" t="n">
         <v>2175000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>737745000</v>
+        <v>824301000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1590051000</v>
+        <v>-1559035000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2327796000</v>
+        <v>2383336000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1159000</v>
+        <v>130570000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1059288000</v>
+        <v>1002496000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1267349000</v>
+        <v>1250270000</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>2734359000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>772000</v>
-      </c>
+        <v>2758360000</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>637948000</v>
+        <v>849824000</v>
       </c>
       <c r="BA2" t="n">
-        <v>154363000</v>
+        <v>241257000</v>
       </c>
       <c r="BB2" t="n">
-        <v>43349000</v>
+        <v>44925000</v>
       </c>
       <c r="BC2" t="n">
-        <v>440236000</v>
+        <v>563642000</v>
       </c>
       <c r="BD2" t="n">
-        <v>54846000</v>
+        <v>64406000</v>
       </c>
       <c r="BE2" t="n">
-        <v>312317000</v>
+        <v>290984000</v>
       </c>
       <c r="BF2" t="n">
-        <v>1728476000</v>
+        <v>1553146000</v>
       </c>
       <c r="BG2" t="n">
-        <v>22032000</v>
+        <v>67669000</v>
       </c>
       <c r="BH2" t="n">
-        <v>1706444000</v>
+        <v>1485477000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1480200000</v>
+        <v>1141936000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>226244000</v>
+        <v>343541000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>8409000</v>
+        <v>8301000</v>
       </c>
       <c r="C3" t="n">
-        <v>234945000</v>
+        <v>235053000</v>
       </c>
       <c r="D3" t="n">
         <v>243354000</v>
       </c>
       <c r="E3" t="n">
-        <v>4181000</v>
+        <v>4416000</v>
       </c>
       <c r="F3" t="n">
-        <v>2781688000</v>
+        <v>2953453000</v>
       </c>
       <c r="G3" t="n">
-        <v>2786313000</v>
+        <v>2959124000</v>
       </c>
       <c r="H3" t="n">
-        <v>1919437000</v>
+        <v>1997999000</v>
       </c>
       <c r="I3" t="n">
-        <v>2781688000</v>
+        <v>2953453000</v>
       </c>
       <c r="J3" t="n">
-        <v>4181000</v>
+        <v>4416000</v>
       </c>
       <c r="K3" t="n">
-        <v>2786313000</v>
+        <v>2959124000</v>
       </c>
       <c r="L3" t="n">
-        <v>2786313000</v>
+        <v>2959124000</v>
       </c>
       <c r="M3" t="n">
-        <v>2786313000</v>
+        <v>2959124000</v>
       </c>
       <c r="N3" t="n">
-        <v>2786313000</v>
+        <v>2959124000</v>
       </c>
       <c r="O3" t="n">
-        <v>-83513000</v>
+        <v>-84645000</v>
       </c>
       <c r="P3" t="n">
-        <v>184913000</v>
+        <v>183516000</v>
       </c>
       <c r="Q3" t="n">
         <v>672777000</v>
@@ -1765,182 +1757,180 @@
         <v>672777000</v>
       </c>
       <c r="S3" t="n">
-        <v>638665000</v>
+        <v>841837000</v>
       </c>
       <c r="T3" t="n">
-        <v>16641000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
+        <v>14052000</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>15572000</v>
+        <v>12813000</v>
       </c>
       <c r="W3" t="n">
-        <v>1069000</v>
+        <v>1239000</v>
       </c>
       <c r="X3" t="n">
-        <v>1069000</v>
+        <v>1239000</v>
       </c>
       <c r="Y3" t="n">
-        <v>622024000</v>
+        <v>827785000</v>
       </c>
       <c r="Z3" t="n">
-        <v>3112000</v>
+        <v>3177000</v>
       </c>
       <c r="AA3" t="n">
-        <v>3112000</v>
+        <v>3177000</v>
       </c>
       <c r="AB3" t="n">
-        <v>594108000</v>
+        <v>750198000</v>
       </c>
       <c r="AC3" t="n">
-        <v>217919000</v>
+        <v>276910000</v>
       </c>
       <c r="AD3" t="n">
-        <v>8850000</v>
+        <v>9291000</v>
       </c>
       <c r="AE3" t="n">
-        <v>367339000</v>
+        <v>463997000</v>
       </c>
       <c r="AF3" t="n">
-        <v>3424978000</v>
+        <v>3800961000</v>
       </c>
       <c r="AG3" t="n">
-        <v>883517000</v>
+        <v>975177000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2485000</v>
+        <v>3841000</v>
       </c>
       <c r="AI3" t="n">
-        <v>14586000</v>
+        <v>884000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>90468000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>118778000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>24023000</v>
+      </c>
       <c r="AL3" t="n">
-        <v>90468000</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>118778000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>722000</v>
+      </c>
       <c r="AN3" t="n">
-        <v>4625000</v>
+        <v>5671000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2450000</v>
+        <v>3496000</v>
       </c>
       <c r="AP3" t="n">
         <v>2175000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>771353000</v>
+        <v>846003000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1537886000</v>
+        <v>-1582254000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2309239000</v>
+        <v>2428257000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2618000</v>
+        <v>5927000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1049350000</v>
+        <v>1099671000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1257271000</v>
+        <v>1322659000</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>2541461000</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
+        <v>2825784000</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>667918000</v>
+        <v>868995000</v>
       </c>
       <c r="BA3" t="n">
-        <v>177295000</v>
+        <v>208668000</v>
       </c>
       <c r="BB3" t="n">
-        <v>40322000</v>
+        <v>45916000</v>
       </c>
       <c r="BC3" t="n">
-        <v>450301000</v>
+        <v>614411000</v>
       </c>
       <c r="BD3" t="n">
-        <v>44618000</v>
+        <v>98972000</v>
       </c>
       <c r="BE3" t="n">
-        <v>302746000</v>
+        <v>316363000</v>
       </c>
       <c r="BF3" t="n">
-        <v>1526179000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>69340000</v>
-      </c>
+        <v>1541454000</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>1456839000</v>
+        <v>1541454000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1139063000</v>
+        <v>1184564000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>317776000</v>
+        <v>356890000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>8301000</v>
+        <v>8409000</v>
       </c>
       <c r="C4" t="n">
-        <v>235053000</v>
+        <v>234945000</v>
       </c>
       <c r="D4" t="n">
         <v>243354000</v>
       </c>
       <c r="E4" t="n">
-        <v>4416000</v>
+        <v>4181000</v>
       </c>
       <c r="F4" t="n">
-        <v>2953453000</v>
+        <v>2781688000</v>
       </c>
       <c r="G4" t="n">
-        <v>2959124000</v>
+        <v>2786313000</v>
       </c>
       <c r="H4" t="n">
-        <v>1997999000</v>
+        <v>1919437000</v>
       </c>
       <c r="I4" t="n">
-        <v>2953453000</v>
+        <v>2781688000</v>
       </c>
       <c r="J4" t="n">
-        <v>4416000</v>
+        <v>4181000</v>
       </c>
       <c r="K4" t="n">
-        <v>2959124000</v>
+        <v>2786313000</v>
       </c>
       <c r="L4" t="n">
-        <v>2959124000</v>
+        <v>2786313000</v>
       </c>
       <c r="M4" t="n">
-        <v>2959124000</v>
+        <v>2786313000</v>
       </c>
       <c r="N4" t="n">
-        <v>2959124000</v>
+        <v>2786313000</v>
       </c>
       <c r="O4" t="n">
-        <v>-84645000</v>
+        <v>-83513000</v>
       </c>
       <c r="P4" t="n">
-        <v>183516000</v>
+        <v>184913000</v>
       </c>
       <c r="Q4" t="n">
         <v>672777000</v>
@@ -1949,175 +1939,183 @@
         <v>672777000</v>
       </c>
       <c r="S4" t="n">
-        <v>841837000</v>
+        <v>638665000</v>
       </c>
       <c r="T4" t="n">
-        <v>14052000</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>16641000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
       <c r="V4" t="n">
-        <v>12813000</v>
+        <v>15572000</v>
       </c>
       <c r="W4" t="n">
-        <v>1239000</v>
+        <v>1069000</v>
       </c>
       <c r="X4" t="n">
-        <v>1239000</v>
+        <v>1069000</v>
       </c>
       <c r="Y4" t="n">
-        <v>827785000</v>
+        <v>622024000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3177000</v>
+        <v>3112000</v>
       </c>
       <c r="AA4" t="n">
-        <v>3177000</v>
+        <v>3112000</v>
       </c>
       <c r="AB4" t="n">
-        <v>750198000</v>
+        <v>594108000</v>
       </c>
       <c r="AC4" t="n">
-        <v>276910000</v>
+        <v>217919000</v>
       </c>
       <c r="AD4" t="n">
-        <v>9291000</v>
+        <v>8850000</v>
       </c>
       <c r="AE4" t="n">
-        <v>463997000</v>
+        <v>367339000</v>
       </c>
       <c r="AF4" t="n">
-        <v>3800961000</v>
+        <v>3424978000</v>
       </c>
       <c r="AG4" t="n">
-        <v>975177000</v>
+        <v>883517000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3841000</v>
+        <v>2485000</v>
       </c>
       <c r="AI4" t="n">
-        <v>884000</v>
+        <v>14586000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>118778000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>24023000</v>
-      </c>
+        <v>90468000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>118778000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>722000</v>
-      </c>
+        <v>90468000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>5671000</v>
+        <v>4625000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3496000</v>
+        <v>2450000</v>
       </c>
       <c r="AP4" t="n">
         <v>2175000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>846003000</v>
+        <v>771353000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1582254000</v>
+        <v>-1537886000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2428257000</v>
+        <v>2309239000</v>
       </c>
       <c r="AT4" t="n">
-        <v>5927000</v>
+        <v>2618000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1099671000</v>
+        <v>1049350000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1322659000</v>
+        <v>1257271000</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>2825784000</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+        <v>2541461000</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ4" t="n">
-        <v>868995000</v>
+        <v>667918000</v>
       </c>
       <c r="BA4" t="n">
-        <v>208668000</v>
+        <v>177295000</v>
       </c>
       <c r="BB4" t="n">
-        <v>45916000</v>
+        <v>40322000</v>
       </c>
       <c r="BC4" t="n">
-        <v>614411000</v>
+        <v>450301000</v>
       </c>
       <c r="BD4" t="n">
-        <v>98972000</v>
+        <v>44618000</v>
       </c>
       <c r="BE4" t="n">
-        <v>316363000</v>
+        <v>302746000</v>
       </c>
       <c r="BF4" t="n">
-        <v>1541454000</v>
-      </c>
-      <c r="BG4" t="inlineStr"/>
+        <v>1526179000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>69340000</v>
+      </c>
       <c r="BH4" t="n">
-        <v>1541454000</v>
+        <v>1456839000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1184564000</v>
+        <v>1139063000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>356890000</v>
+        <v>317776000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45473</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8583000</v>
+      </c>
       <c r="C5" t="n">
-        <v>243354000</v>
+        <v>234822000</v>
       </c>
       <c r="D5" t="n">
         <v>243354000</v>
       </c>
       <c r="E5" t="n">
-        <v>5212000</v>
+        <v>3948000</v>
       </c>
       <c r="F5" t="n">
-        <v>2875466000</v>
+        <v>2895693000</v>
       </c>
       <c r="G5" t="n">
-        <v>2880665000</v>
+        <v>2904223000</v>
       </c>
       <c r="H5" t="n">
-        <v>1980576000</v>
+        <v>2116164000</v>
       </c>
       <c r="I5" t="n">
-        <v>2875466000</v>
+        <v>2895693000</v>
       </c>
       <c r="J5" t="n">
-        <v>5212000</v>
+        <v>3948000</v>
       </c>
       <c r="K5" t="n">
-        <v>2880665000</v>
+        <v>2904223000</v>
       </c>
       <c r="L5" t="n">
-        <v>2880665000</v>
+        <v>2904223000</v>
       </c>
       <c r="M5" t="n">
-        <v>2880665000</v>
+        <v>2904223000</v>
       </c>
       <c r="N5" t="n">
-        <v>2880665000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+        <v>2904223000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-85104000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>187830000</v>
+      </c>
       <c r="Q5" t="n">
         <v>672777000</v>
       </c>
@@ -2125,130 +2123,132 @@
         <v>672777000</v>
       </c>
       <c r="S5" t="n">
-        <v>794877000</v>
+        <v>642374000</v>
       </c>
       <c r="T5" t="n">
-        <v>17093000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>24179000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1943000</v>
+      </c>
       <c r="V5" t="n">
-        <v>15246000</v>
+        <v>20903000</v>
       </c>
       <c r="W5" t="n">
-        <v>1847000</v>
+        <v>1333000</v>
       </c>
       <c r="X5" t="n">
-        <v>1847000</v>
+        <v>1333000</v>
       </c>
       <c r="Y5" t="n">
-        <v>777784000</v>
+        <v>618195000</v>
       </c>
       <c r="Z5" t="n">
-        <v>3365000</v>
+        <v>2615000</v>
       </c>
       <c r="AA5" t="n">
-        <v>3365000</v>
+        <v>2615000</v>
       </c>
       <c r="AB5" t="n">
-        <v>733338000</v>
+        <v>595459000</v>
       </c>
       <c r="AC5" t="n">
-        <v>312560000</v>
+        <v>274193000</v>
       </c>
       <c r="AD5" t="n">
-        <v>12772000</v>
+        <v>17389000</v>
       </c>
       <c r="AE5" t="n">
-        <v>408006000</v>
+        <v>303877000</v>
       </c>
       <c r="AF5" t="n">
-        <v>3675542000</v>
+        <v>3546597000</v>
       </c>
       <c r="AG5" t="n">
-        <v>917182000</v>
+        <v>812238000</v>
       </c>
       <c r="AH5" t="n">
-        <v>4250000</v>
+        <v>1702000</v>
       </c>
       <c r="AI5" t="n">
-        <v>672000</v>
+        <v>11897000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>82760000</v>
+        <v>52364000</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>81945000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>815000</v>
-      </c>
+        <v>52092000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>5199000</v>
+        <v>8530000</v>
       </c>
       <c r="AO5" t="n">
-        <v>3024000</v>
+        <v>6355000</v>
       </c>
       <c r="AP5" t="n">
         <v>2175000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>824301000</v>
+        <v>737745000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1559035000</v>
+        <v>-1590051000</v>
       </c>
       <c r="AS5" t="n">
-        <v>2383336000</v>
+        <v>2327796000</v>
       </c>
       <c r="AT5" t="n">
-        <v>130570000</v>
+        <v>1159000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1002496000</v>
+        <v>1059288000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1250270000</v>
+        <v>1267349000</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>2758360000</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+        <v>2734359000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>772000</v>
+      </c>
       <c r="AZ5" t="n">
-        <v>849824000</v>
+        <v>637948000</v>
       </c>
       <c r="BA5" t="n">
-        <v>241257000</v>
+        <v>154363000</v>
       </c>
       <c r="BB5" t="n">
-        <v>44925000</v>
+        <v>43349000</v>
       </c>
       <c r="BC5" t="n">
-        <v>563642000</v>
+        <v>440236000</v>
       </c>
       <c r="BD5" t="n">
-        <v>64406000</v>
+        <v>54846000</v>
       </c>
       <c r="BE5" t="n">
-        <v>290984000</v>
+        <v>312317000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1553146000</v>
+        <v>1728476000</v>
       </c>
       <c r="BG5" t="n">
-        <v>67669000</v>
+        <v>22032000</v>
       </c>
       <c r="BH5" t="n">
-        <v>1485477000</v>
+        <v>1706444000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1141936000</v>
+        <v>1480200000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>343541000</v>
+        <v>226244000</v>
       </c>
     </row>
   </sheetData>
@@ -2464,486 +2464,486 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>198271000</v>
+        <v>90508000</v>
       </c>
       <c r="C2" t="n">
-        <v>-1444000</v>
+        <v>-15452000</v>
       </c>
       <c r="D2" t="n">
-        <v>-40419000</v>
+        <v>-140136000</v>
       </c>
       <c r="E2" t="n">
-        <v>768457000</v>
+        <v>1277330000</v>
       </c>
       <c r="F2" t="n">
-        <v>730182000</v>
+        <v>1337336000</v>
       </c>
       <c r="G2" t="n">
-        <v>-2643000</v>
+        <v>117062000</v>
       </c>
       <c r="H2" t="n">
-        <v>40918000</v>
+        <v>-177068000</v>
       </c>
       <c r="I2" t="n">
-        <v>-83515000</v>
+        <v>-129186000</v>
       </c>
       <c r="J2" t="n">
-        <v>-254000</v>
+        <v>-283000</v>
       </c>
       <c r="K2" t="n">
-        <v>-77501000</v>
+        <v>-108954000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1444000</v>
+        <v>-15452000</v>
       </c>
       <c r="M2" t="n">
-        <v>-1444000</v>
+        <v>-15452000</v>
       </c>
       <c r="N2" t="n">
-        <v>-114257000</v>
+        <v>-278526000</v>
       </c>
       <c r="O2" t="n">
-        <v>43667000</v>
+        <v>29781000</v>
       </c>
       <c r="P2" t="n">
-        <v>5087000</v>
+        <v>2130000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-123250000</v>
+        <v>-170621000</v>
       </c>
       <c r="R2" t="n">
-        <v>88080000</v>
+        <v>4237000</v>
       </c>
       <c r="S2" t="n">
-        <v>-211330000</v>
+        <v>-174858000</v>
       </c>
       <c r="T2" t="n">
-        <v>-39761000</v>
+        <v>-139816000</v>
       </c>
       <c r="U2" t="n">
-        <v>658000</v>
+        <v>320000</v>
       </c>
       <c r="V2" t="n">
-        <v>-40419000</v>
+        <v>-140136000</v>
       </c>
       <c r="W2" t="n">
-        <v>238690000</v>
+        <v>230644000</v>
       </c>
       <c r="X2" t="n">
-        <v>-27425000</v>
+        <v>-93195000</v>
       </c>
       <c r="Y2" t="n">
-        <v>643000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2059000</v>
-      </c>
+        <v>-130026000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>-3565000</v>
+        <v>-7469000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-8298000</v>
+        <v>15227000</v>
       </c>
       <c r="AC2" t="n">
-        <v>31202000</v>
+        <v>-147016000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-20755000</v>
+        <v>9232000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-43805000</v>
+        <v>-26524000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-147000</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="AH2" t="n">
-        <v>72401000</v>
+        <v>62914000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1329000</v>
+        <v>3242000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>71072000</v>
+        <v>59672000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-5859000</v>
+        <v>-3535000</v>
       </c>
       <c r="AL2" t="n">
-        <v>632000</v>
+        <v>-6169000</v>
       </c>
       <c r="AM2" t="n">
-        <v>2000</v>
+        <v>2608000</v>
       </c>
       <c r="AN2" t="n">
-        <v>244557000</v>
+        <v>420753000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>109269000</v>
+        <v>161803000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1064000</v>
+        <v>-18636000</v>
       </c>
       <c r="D3" t="n">
-        <v>-49445000</v>
+        <v>-107692000</v>
       </c>
       <c r="E3" t="n">
-        <v>730182000</v>
+        <v>1009960000</v>
       </c>
       <c r="F3" t="n">
-        <v>1009960000</v>
+        <v>1277330000</v>
       </c>
       <c r="G3" t="n">
-        <v>-79491000</v>
+        <v>-29519000</v>
       </c>
       <c r="H3" t="n">
-        <v>-200287000</v>
+        <v>-237851000</v>
       </c>
       <c r="I3" t="n">
-        <v>-106827000</v>
+        <v>-136927000</v>
       </c>
       <c r="J3" t="n">
-        <v>-208000</v>
+        <v>-296000</v>
       </c>
       <c r="K3" t="n">
-        <v>-101034000</v>
+        <v>-113211000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1064000</v>
+        <v>-18636000</v>
       </c>
       <c r="M3" t="n">
-        <v>-1064000</v>
+        <v>-18636000</v>
       </c>
       <c r="N3" t="n">
-        <v>-252174000</v>
+        <v>-370419000</v>
       </c>
       <c r="O3" t="n">
-        <v>28348000</v>
+        <v>23620000</v>
       </c>
       <c r="P3" t="n">
-        <v>6414000</v>
+        <v>4963000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-238614000</v>
+        <v>-291776000</v>
       </c>
       <c r="R3" t="n">
-        <v>67998000</v>
+        <v>74177000</v>
       </c>
       <c r="S3" t="n">
-        <v>-306612000</v>
+        <v>-365953000</v>
       </c>
       <c r="T3" t="n">
-        <v>-48322000</v>
+        <v>-107226000</v>
       </c>
       <c r="U3" t="n">
-        <v>1123000</v>
+        <v>466000</v>
       </c>
       <c r="V3" t="n">
-        <v>-49445000</v>
+        <v>-107692000</v>
       </c>
       <c r="W3" t="n">
-        <v>158714000</v>
+        <v>269495000</v>
       </c>
       <c r="X3" t="n">
-        <v>-16614000</v>
+        <v>-34443000</v>
       </c>
       <c r="Y3" t="n">
-        <v>38127000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
+        <v>-21997000</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>-47685000</v>
+        <v>35906000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-104552000</v>
+        <v>48615000</v>
       </c>
       <c r="AC3" t="n">
-        <v>139425000</v>
+        <v>-42657000</v>
       </c>
       <c r="AD3" t="n">
-        <v>50939000</v>
+        <v>-63861000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-32570000</v>
+        <v>-24286000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2196000</v>
+        <v>2537000</v>
       </c>
       <c r="AG3" t="n">
-        <v>9000</v>
+        <v>-54000</v>
       </c>
       <c r="AH3" t="n">
-        <v>76635000</v>
+        <v>65977000</v>
       </c>
       <c r="AI3" t="n">
-        <v>971000</v>
+        <v>962000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75664000</v>
+        <v>65015000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-4710000</v>
+        <v>-5262000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1252000</v>
+        <v>1358000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-539000</v>
+        <v>-127000</v>
       </c>
       <c r="AN3" t="n">
-        <v>90571000</v>
+        <v>285431000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>161803000</v>
+        <v>109269000</v>
       </c>
       <c r="C4" t="n">
-        <v>-18636000</v>
+        <v>-1064000</v>
       </c>
       <c r="D4" t="n">
-        <v>-107692000</v>
+        <v>-49445000</v>
       </c>
       <c r="E4" t="n">
+        <v>730182000</v>
+      </c>
+      <c r="F4" t="n">
         <v>1009960000</v>
       </c>
-      <c r="F4" t="n">
-        <v>1277330000</v>
-      </c>
       <c r="G4" t="n">
-        <v>-29519000</v>
+        <v>-79491000</v>
       </c>
       <c r="H4" t="n">
-        <v>-237851000</v>
+        <v>-200287000</v>
       </c>
       <c r="I4" t="n">
-        <v>-136927000</v>
+        <v>-106827000</v>
       </c>
       <c r="J4" t="n">
-        <v>-296000</v>
+        <v>-208000</v>
       </c>
       <c r="K4" t="n">
-        <v>-113211000</v>
+        <v>-101034000</v>
       </c>
       <c r="L4" t="n">
-        <v>-18636000</v>
+        <v>-1064000</v>
       </c>
       <c r="M4" t="n">
-        <v>-18636000</v>
+        <v>-1064000</v>
       </c>
       <c r="N4" t="n">
-        <v>-370419000</v>
+        <v>-252174000</v>
       </c>
       <c r="O4" t="n">
-        <v>23620000</v>
+        <v>28348000</v>
       </c>
       <c r="P4" t="n">
-        <v>4963000</v>
+        <v>6414000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-291776000</v>
+        <v>-238614000</v>
       </c>
       <c r="R4" t="n">
-        <v>74177000</v>
+        <v>67998000</v>
       </c>
       <c r="S4" t="n">
-        <v>-365953000</v>
+        <v>-306612000</v>
       </c>
       <c r="T4" t="n">
-        <v>-107226000</v>
+        <v>-48322000</v>
       </c>
       <c r="U4" t="n">
-        <v>466000</v>
+        <v>1123000</v>
       </c>
       <c r="V4" t="n">
-        <v>-107692000</v>
+        <v>-49445000</v>
       </c>
       <c r="W4" t="n">
-        <v>269495000</v>
+        <v>158714000</v>
       </c>
       <c r="X4" t="n">
-        <v>-34443000</v>
+        <v>-16614000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-21997000</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>38127000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
       <c r="AA4" t="n">
-        <v>35906000</v>
+        <v>-47685000</v>
       </c>
       <c r="AB4" t="n">
-        <v>48615000</v>
+        <v>-104552000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-42657000</v>
+        <v>139425000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-63861000</v>
+        <v>50939000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-24286000</v>
+        <v>-32570000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2537000</v>
+        <v>2196000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-54000</v>
+        <v>9000</v>
       </c>
       <c r="AH4" t="n">
-        <v>65977000</v>
+        <v>76635000</v>
       </c>
       <c r="AI4" t="n">
-        <v>962000</v>
+        <v>971000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>65015000</v>
+        <v>75664000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-5262000</v>
+        <v>-4710000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1358000</v>
+        <v>1252000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-127000</v>
+        <v>-539000</v>
       </c>
       <c r="AN4" t="n">
-        <v>285431000</v>
+        <v>90571000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>90508000</v>
+        <v>198271000</v>
       </c>
       <c r="C5" t="n">
-        <v>-15452000</v>
+        <v>-1444000</v>
       </c>
       <c r="D5" t="n">
-        <v>-140136000</v>
+        <v>-40419000</v>
       </c>
       <c r="E5" t="n">
-        <v>1277330000</v>
+        <v>768457000</v>
       </c>
       <c r="F5" t="n">
-        <v>1337336000</v>
+        <v>730182000</v>
       </c>
       <c r="G5" t="n">
-        <v>117062000</v>
+        <v>-2643000</v>
       </c>
       <c r="H5" t="n">
-        <v>-177068000</v>
+        <v>40918000</v>
       </c>
       <c r="I5" t="n">
-        <v>-129186000</v>
+        <v>-83515000</v>
       </c>
       <c r="J5" t="n">
-        <v>-283000</v>
+        <v>-254000</v>
       </c>
       <c r="K5" t="n">
-        <v>-108954000</v>
+        <v>-77501000</v>
       </c>
       <c r="L5" t="n">
-        <v>-15452000</v>
+        <v>-1444000</v>
       </c>
       <c r="M5" t="n">
-        <v>-15452000</v>
+        <v>-1444000</v>
       </c>
       <c r="N5" t="n">
-        <v>-278526000</v>
+        <v>-114257000</v>
       </c>
       <c r="O5" t="n">
-        <v>29781000</v>
+        <v>43667000</v>
       </c>
       <c r="P5" t="n">
-        <v>2130000</v>
+        <v>5087000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-170621000</v>
+        <v>-123250000</v>
       </c>
       <c r="R5" t="n">
-        <v>4237000</v>
+        <v>88080000</v>
       </c>
       <c r="S5" t="n">
-        <v>-174858000</v>
+        <v>-211330000</v>
       </c>
       <c r="T5" t="n">
-        <v>-139816000</v>
+        <v>-39761000</v>
       </c>
       <c r="U5" t="n">
-        <v>320000</v>
+        <v>658000</v>
       </c>
       <c r="V5" t="n">
-        <v>-140136000</v>
+        <v>-40419000</v>
       </c>
       <c r="W5" t="n">
-        <v>230644000</v>
+        <v>238690000</v>
       </c>
       <c r="X5" t="n">
-        <v>-93195000</v>
+        <v>-27425000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-130026000</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>643000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2059000</v>
+      </c>
       <c r="AA5" t="n">
-        <v>-7469000</v>
+        <v>-3565000</v>
       </c>
       <c r="AB5" t="n">
-        <v>15227000</v>
+        <v>-8298000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-147016000</v>
+        <v>31202000</v>
       </c>
       <c r="AD5" t="n">
-        <v>9232000</v>
+        <v>-20755000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-26524000</v>
+        <v>-43805000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-147000</v>
       </c>
       <c r="AG5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>72401000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1329000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>71072000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-5859000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>632000</v>
+      </c>
+      <c r="AM5" t="n">
         <v>2000</v>
       </c>
-      <c r="AH5" t="n">
-        <v>62914000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>3242000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>59672000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-3535000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-6169000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>2608000</v>
-      </c>
       <c r="AN5" t="n">
-        <v>420753000</v>
+        <v>244557000</v>
       </c>
     </row>
   </sheetData>
@@ -3503,187 +3503,187 @@
       </c>
       <c r="DE1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
@@ -3786,34 +3786,34 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>11.98</v>
+        <v>11</v>
       </c>
       <c r="V2" t="n">
-        <v>11.81</v>
+        <v>11</v>
       </c>
       <c r="W2" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="X2" t="n">
-        <v>11.81</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.98</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.81</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.81</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
         <v>0.48</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.01</v>
+        <v>4.36</v>
       </c>
       <c r="AE2" t="n">
         <v>1773100800</v>
@@ -3825,31 +3825,31 @@
         <v>4.04</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.2</v>
+        <v>0.202</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.661289999999999</v>
+        <v>8.870968</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4125</v>
+        <v>3000</v>
       </c>
       <c r="AK2" t="n">
-        <v>4125</v>
+        <v>3000</v>
       </c>
       <c r="AL2" t="n">
-        <v>5278</v>
+        <v>6757</v>
       </c>
       <c r="AM2" t="n">
-        <v>1212</v>
+        <v>13100</v>
       </c>
       <c r="AN2" t="n">
-        <v>1212</v>
+        <v>13100</v>
       </c>
       <c r="AO2" t="n">
-        <v>11.32</v>
+        <v>10.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.8</v>
+        <v>11.3</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -3858,16 +3858,16 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2810915328</v>
+        <v>2580974080</v>
       </c>
       <c r="AT2" t="n">
-        <v>2810915320</v>
+        <v>2580974000</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
         <v>17</v>
@@ -3876,19 +3876,19 @@
         <v>1</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.5834682</v>
+        <v>0.53573877</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5206</v>
+        <v>12.2576</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.9208</v>
+        <v>11.96425</v>
       </c>
       <c r="BB2" t="n">
         <v>0.48</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.04006678</v>
+        <v>0.043636363</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>862663296</v>
+        <v>632721984</v>
       </c>
       <c r="BG2" t="n">
         <v>0.060349997</v>
@@ -3923,7 +3923,7 @@
         <v>13.931</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.8599526</v>
+        <v>0.7896059</v>
       </c>
       <c r="BO2" t="n">
         <v>1751241600</v>
@@ -3944,16 +3944,16 @@
         <v>1.24</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.179</v>
+        <v>0.131</v>
       </c>
       <c r="BV2" t="n">
-        <v>2.58</v>
+        <v>1.892</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.1301887</v>
+        <v>0.100000024</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BY2" t="n">
         <v>0.15</v>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>11.98</v>
+        <v>11</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -4069,140 +4069,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DE2" t="n">
-        <v>-0.5406008</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>-0.043176904</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.059199333</v>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>LAM SOON (HK)</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Lam Soon (Hong Kong) Limited</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DH2" t="n">
-        <v>0.0049660536</v>
-      </c>
-      <c r="DI2" t="n">
+        <v>1781682158</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>finmb_8192151</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>11.0 - 11.0</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>6757</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>10.0 - 13.0</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.15384616</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>10.000002</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1739958833</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1739958833</v>
+      </c>
+      <c r="EC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-1.2575998</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.10259756</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.9642496</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.08059424</v>
+      </c>
+      <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="EJ2" t="n">
         <v>15</v>
       </c>
-      <c r="DK2" t="b">
+      <c r="EK2" t="b">
         <v>0</v>
       </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
+      <c r="EL2" t="n">
         <v>947554200000</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>11.8 - 11.81</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>5278</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1.9799995</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.19799995</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>10.0 - 17.0</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>-5.0200005</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.29529414</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>13.01887</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1739958833</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1739958833</v>
-      </c>
-      <c r="DZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>1780290544</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>finmb_8192151</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>LAM SOON (HK)</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>Lam Soon (Hong Kong) Limited</t>
-        </is>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>11.98</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="EO2" t="b">
+        <v>0</v>
       </c>
       <c r="EP2" t="inlineStr"/>
     </row>
